--- a/data/trans_dic/IP42B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>La persona sustentadora principal recibe una pensión</t>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,85</t>
+          <t>0,0; 24,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 31,26</t>
+          <t>2,8; 28,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 26,36</t>
+          <t>2,66; 29,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,69</t>
+          <t>0,0; 17,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,21</t>
+          <t>0,0; 20,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,62</t>
+          <t>0,0; 20,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 15,17</t>
+          <t>1,6; 15,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 18,34</t>
+          <t>2,07; 18,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 17,31</t>
+          <t>3,04; 17,63</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 35,34</t>
+          <t>4,26; 35,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,2</t>
+          <t>0,0; 17,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,42</t>
+          <t>0,0; 32,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,4</t>
+          <t>0,0; 27,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 20,65</t>
+          <t>2,35; 21,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,15</t>
+          <t>0,0; 17,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 24,98</t>
+          <t>4,35; 24,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 15,16</t>
+          <t>2,63; 15,9</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,19</t>
+          <t>0,0; 15,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,19</t>
+          <t>1,39; 12,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,67</t>
+          <t>0,0; 18,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,44</t>
+          <t>0,0; 12,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 23,47</t>
+          <t>4,45; 25,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 19,94</t>
+          <t>1,64; 16,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,13</t>
+          <t>1,05; 8,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 14,69</t>
+          <t>3,15; 13,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,72</t>
+          <t>1,29; 12,06</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 13,69</t>
+          <t>1,25; 11,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 26,75</t>
+          <t>10,05; 28,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 13,5</t>
+          <t>3,12; 14,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,24</t>
+          <t>2,14; 11,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 16,84</t>
+          <t>4,54; 16,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,47</t>
+          <t>1,76; 10,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,49</t>
+          <t>2,43; 9,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 18,37</t>
+          <t>8,12; 18,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,71</t>
+          <t>2,9; 9,62</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 44,9</t>
+          <t>4,87; 41,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 29,93</t>
+          <t>10,98; 29,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 14,25</t>
+          <t>3,39; 15,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 27,34</t>
+          <t>2,93; 26,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,22; 34,86</t>
+          <t>14,18; 36,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 13,15</t>
+          <t>2,15; 12,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 26,12</t>
+          <t>7,14; 26,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,22; 28,18</t>
+          <t>14,33; 28,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,77</t>
+          <t>3,5; 11,16</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1228,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,28; 85,7</t>
+          <t>13,28; 86,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,42; 81,17</t>
+          <t>17,45; 76,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,26; 49,04</t>
+          <t>6,38; 51,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1247,27 +1248,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,86; 62,86</t>
+          <t>11,14; 59,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,46; 62,97</t>
+          <t>13,36; 59,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,07; 75,8</t>
+          <t>24,44; 82,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,7; 62,98</t>
+          <t>21,63; 61,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,16; 48,99</t>
+          <t>16,12; 49,23</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,57</t>
+          <t>5,13; 12,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 20,82</t>
+          <t>11,38; 20,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,18</t>
+          <t>4,93; 11,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,11</t>
+          <t>3,96; 10,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,85; 18,54</t>
+          <t>9,84; 18,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,65</t>
+          <t>4,82; 10,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,13</t>
+          <t>5,08; 10,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,0; 18,1</t>
+          <t>12,16; 18,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,7</t>
+          <t>5,5; 9,84</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La persona sustentadora principal recibe una pensión (tasa de respuesta: 28,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2179</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3173</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4703</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>464; 4757</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>462; 5062</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3483</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3255</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4398</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>617; 5871</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>667; 5904</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1176; 6811</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1573</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>616; 5160</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4608</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4509</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4355</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>602; 5541</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4829</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1327; 7463</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1366; 8264</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4451</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>479; 4461</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4422</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4454</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1300; 7305</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>591; 5856</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>695; 5851</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2007; 8847</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>771; 7203</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2686</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9304</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3917</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15703</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7585</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>661; 6146</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5386; 15083</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1805; 8497</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1315; 6906</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3127; 11036</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1377; 8141</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2772; 10953</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9944; 22878</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3947; 13090</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8854</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4530</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10034</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5649</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18888</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>712; 6104</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5184; 13865</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026; 9516</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>705; 6278</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6178; 15690</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1237; 6948</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2762; 10066</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>13006; 25749</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4115; 13101</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2657</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3716</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4077</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>6753</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>645; 4176</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1399; 6105</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>697; 5645</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2744</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1026; 5487</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1260; 5656</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2008; 6780</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3726; 10557</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3280; 10018</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>11156</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>27514</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15016</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10385</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>25044</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>16171</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>21541</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>52558</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>31187</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>6872; 17140</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>19850; 35649</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9656; 22160</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6313; 16299</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>17957; 34054</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10999; 23971</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>14899; 29830</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>43396; 64429</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>23349; 41725</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP42B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,85</t>
+          <t>0,0; 24,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 28,69</t>
+          <t>2,83; 31,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 29,12</t>
+          <t>2,66; 27,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,67</t>
+          <t>0,0; 17,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,79</t>
+          <t>0,0; 21,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 21,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 15,2</t>
+          <t>0,64; 13,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 18,32</t>
+          <t>2,11; 20,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 17,63</t>
+          <t>3,1; 18,39</t>
         </is>
       </c>
     </row>
@@ -793,42 +793,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 35,72</t>
+          <t>4,28; 35,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,48</t>
+          <t>0,0; 18,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,09</t>
+          <t>0,0; 29,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,13</t>
+          <t>0,0; 30,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 21,64</t>
+          <t>2,35; 20,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,42</t>
+          <t>0,0; 16,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 24,47</t>
+          <t>4,11; 23,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 15,9</t>
+          <t>2,35; 14,77</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,25</t>
+          <t>0,0; 16,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,91</t>
+          <t>1,37; 14,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,71</t>
+          <t>0,0; 16,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,1</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 25,0</t>
+          <t>4,44; 23,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 16,23</t>
+          <t>1,64; 16,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,87</t>
+          <t>1,04; 8,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,87</t>
+          <t>3,9; 15,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 12,06</t>
+          <t>1,29; 11,45</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,63</t>
+          <t>1,28; 12,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 28,13</t>
+          <t>10,2; 26,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 14,67</t>
+          <t>3,0; 14,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 11,24</t>
+          <t>1,13; 11,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 16,03</t>
+          <t>4,49; 16,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,41</t>
+          <t>1,66; 10,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,59</t>
+          <t>2,83; 9,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 18,68</t>
+          <t>8,03; 18,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,62</t>
+          <t>3,07; 9,52</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 41,77</t>
+          <t>4,83; 42,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,98; 29,36</t>
+          <t>11,04; 30,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,91</t>
+          <t>3,26; 14,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 26,1</t>
+          <t>3,23; 26,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,18; 36,02</t>
+          <t>14,53; 35,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,06</t>
+          <t>2,29; 12,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 26,03</t>
+          <t>7,31; 26,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 28,36</t>
+          <t>14,53; 28,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 11,16</t>
+          <t>3,73; 11,69</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,28; 86,02</t>
+          <t>25,0; 85,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,45; 76,16</t>
+          <t>17,44; 75,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 51,71</t>
+          <t>6,57; 50,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,62</t>
+          <t>0,0; 98,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 59,57</t>
+          <t>11,69; 62,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,36; 59,96</t>
+          <t>13,2; 62,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,44; 82,52</t>
+          <t>24,48; 76,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,63; 61,28</t>
+          <t>21,19; 61,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,12; 49,23</t>
+          <t>15,98; 47,15</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 12,78</t>
+          <t>4,96; 12,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,38; 20,44</t>
+          <t>11,93; 20,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,3</t>
+          <t>5,07; 11,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 10,22</t>
+          <t>3,84; 10,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,65</t>
+          <t>9,81; 18,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,5</t>
+          <t>4,66; 10,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,16</t>
+          <t>4,98; 10,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,16; 18,05</t>
+          <t>11,84; 17,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,84</t>
+          <t>5,63; 9,76</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4703</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>464; 4757</t>
+          <t>470; 5153</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>462; 5062</t>
+          <t>462; 4775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 3476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3255</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4398</t>
+          <t>0; 4627</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>617; 5871</t>
+          <t>248; 5349</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>667; 5904</t>
+          <t>680; 6542</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1176; 6811</t>
+          <t>1197; 7104</t>
         </is>
       </c>
     </row>
@@ -1807,42 +1807,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>616; 5160</t>
+          <t>618; 5122</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4608</t>
+          <t>0; 4815</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4509</t>
+          <t>0; 4087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4355</t>
+          <t>0; 4904</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>602; 5541</t>
+          <t>603; 5173</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1327; 7463</t>
+          <t>1254; 7290</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1366; 8264</t>
+          <t>1222; 7677</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4451</t>
+          <t>0; 4738</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>479; 4461</t>
+          <t>472; 4966</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 4005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4454</t>
+          <t>0; 3447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1300; 7305</t>
+          <t>1297; 6810</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>591; 5856</t>
+          <t>590; 5957</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>695; 5851</t>
+          <t>689; 5754</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2007; 8847</t>
+          <t>2488; 9814</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>771; 7203</t>
+          <t>768; 6835</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>661; 6146</t>
+          <t>674; 6501</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5386; 15083</t>
+          <t>5467; 14389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1805; 8497</t>
+          <t>1741; 8148</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1315; 6906</t>
+          <t>695; 6754</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3127; 11036</t>
+          <t>3089; 11576</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1377; 8141</t>
+          <t>1295; 8147</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2772; 10953</t>
+          <t>3236; 10980</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9944; 22878</t>
+          <t>9831; 22302</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3947; 13090</t>
+          <t>4173; 12960</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>712; 6104</t>
+          <t>706; 6212</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5184; 13865</t>
+          <t>5214; 14307</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026; 9516</t>
+          <t>1952; 8837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>705; 6278</t>
+          <t>776; 6356</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6178; 15690</t>
+          <t>6329; 15392</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1237; 6948</t>
+          <t>1319; 7439</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2762; 10066</t>
+          <t>2827; 10252</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13006; 25749</t>
+          <t>13190; 25609</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4115; 13101</t>
+          <t>4383; 13721</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>645; 4176</t>
+          <t>1214; 4171</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1399; 6105</t>
+          <t>1398; 6027</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>697; 5645</t>
+          <t>718; 5475</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2744</t>
+          <t>0; 3316</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1026; 5487</t>
+          <t>1076; 5770</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1260; 5656</t>
+          <t>1245; 5858</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2008; 6780</t>
+          <t>2012; 6259</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3726; 10557</t>
+          <t>3650; 10544</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3280; 10018</t>
+          <t>3253; 9595</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6872; 17140</t>
+          <t>6651; 17293</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19850; 35649</t>
+          <t>20800; 36540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9656; 22160</t>
+          <t>9935; 21708</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6313; 16299</t>
+          <t>6124; 16677</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17957; 34054</t>
+          <t>17902; 33282</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10999; 23971</t>
+          <t>10631; 23642</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14899; 29830</t>
+          <t>14609; 29907</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43396; 64429</t>
+          <t>42257; 63283</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23349; 41725</t>
+          <t>23892; 41408</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP42B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP42B-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,81%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,82%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,69</t>
+          <t>0,0; 17,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 31,08</t>
+          <t>0,0; 22,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 27,47</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,64</t>
+          <t>0,0; 23,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,72</t>
+          <t>2,83; 31,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,77</t>
+          <t>2,59; 26,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 13,84</t>
+          <t>1,65; 15,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 20,29</t>
+          <t>2,28; 18,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 18,39</t>
+          <t>2,71; 17,31</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>13,5%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,22%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 29,42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 28,4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2,37; 20,65</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,28; 35,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 18,27</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,09</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,55</t>
+          <t>4,22; 35,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 20,2</t>
+          <t>0,0; 17,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,94</t>
+          <t>0,0; 17,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 23,91</t>
+          <t>4,16; 24,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,77</t>
+          <t>2,62; 15,16</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,24</t>
+          <t>0,0; 9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 14,37</t>
+          <t>4,5; 23,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,95</t>
+          <t>1,65; 19,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 17,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 23,3</t>
+          <t>1,37; 13,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 16,51</t>
+          <t>0,0; 17,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,72</t>
+          <t>1,05; 9,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 15,39</t>
+          <t>3,86; 14,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,45</t>
+          <t>1,27; 11,72</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 12,31</t>
+          <t>2,17; 12,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 26,84</t>
+          <t>4,77; 16,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 14,06</t>
+          <t>1,7; 10,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 11,0</t>
+          <t>2,08; 13,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 16,81</t>
+          <t>9,95; 26,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,42</t>
+          <t>3,08; 13,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 9,61</t>
+          <t>2,42; 9,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 18,21</t>
+          <t>8,06; 18,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,52</t>
+          <t>3,06; 9,71</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23,03%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>19,57%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>18,75%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,58%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 42,51</t>
+          <t>3,85; 27,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 30,3</t>
+          <t>13,22; 34,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 14,78</t>
+          <t>2,13; 13,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 26,42</t>
+          <t>4,76; 44,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 35,33</t>
+          <t>11,11; 29,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 12,91</t>
+          <t>3,13; 14,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 26,51</t>
+          <t>7,05; 26,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 28,21</t>
+          <t>14,22; 28,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 11,69</t>
+          <t>3,35; 10,77</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>32,97%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34,85%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>54,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>46,36%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>24,98%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,0; 85,91</t>
+          <t>0,0; 81,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,44; 75,19</t>
+          <t>11,86; 62,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 50,14</t>
+          <t>13,46; 62,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 98,62</t>
+          <t>13,28; 85,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,69; 62,64</t>
+          <t>17,42; 81,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,2; 62,11</t>
+          <t>6,26; 49,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,48; 76,18</t>
+          <t>24,07; 75,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,19; 61,21</t>
+          <t>21,7; 62,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,98; 47,15</t>
+          <t>16,16; 48,99</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,32%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>15,77%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7,66%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 12,9</t>
+          <t>3,88; 10,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,93; 20,95</t>
+          <t>9,85; 18,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,07; 11,07</t>
+          <t>4,55; 10,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,46</t>
+          <t>4,79; 12,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,81; 18,23</t>
+          <t>11,7; 20,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,36</t>
+          <t>4,84; 11,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,19</t>
+          <t>5,18; 10,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 17,73</t>
+          <t>12,0; 18,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,76</t>
+          <t>5,57; 9,7</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1479</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1886</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1707</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1466</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>0; 3485</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>470; 5153</t>
+          <t>0; 3476</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>462; 4775</t>
+          <t>0; 4383</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 4514</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>469; 5182</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4627</t>
+          <t>450; 4581</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>248; 5349</t>
+          <t>636; 5862</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>680; 6542</t>
+          <t>734; 5911</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1197; 7104</t>
+          <t>1049; 6689</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1573</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1376</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1573</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2125</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 4134</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4558</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>608; 5288</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>618; 5122</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4815</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4087</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4904</t>
+          <t>609; 5104</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>603; 5173</t>
+          <t>0; 4533</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4754</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1254; 7290</t>
+          <t>1269; 7619</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1222; 7677</t>
+          <t>1362; 7876</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1475</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1805</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>759</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3334</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2221</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4738</t>
+          <t>0; 3476</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>472; 4966</t>
+          <t>1314; 6860</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>597; 7194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3447</t>
+          <t>0; 5017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1297; 6810</t>
+          <t>474; 4556</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>590; 5957</t>
+          <t>0; 4176</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>689; 5754</t>
+          <t>693; 6029</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2488; 9814</t>
+          <t>2462; 9367</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>768; 6835</t>
+          <t>759; 6999</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2686</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9304</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3917</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6398</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3668</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>674; 6501</t>
+          <t>1330; 7518</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5467; 14389</t>
+          <t>3283; 11595</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1741; 8148</t>
+          <t>1330; 8185</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>695; 6754</t>
+          <t>1100; 7234</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3089; 11576</t>
+          <t>5334; 14339</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1295; 8147</t>
+          <t>1782; 7820</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3236; 10980</t>
+          <t>2764; 10846</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9831; 22302</t>
+          <t>9870; 22502</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4173; 12960</t>
+          <t>4159; 13223</t>
         </is>
       </c>
     </row>
@@ -2190,27 +2190,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10034</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2859</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>8854</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4530</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2789</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10034</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>706; 6212</t>
+          <t>926; 6577</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5214; 14307</t>
+          <t>5760; 15187</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1952; 8837</t>
+          <t>1225; 7574</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>776; 6356</t>
+          <t>695; 6561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6329; 15392</t>
+          <t>5244; 14135</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1319; 7439</t>
+          <t>1869; 8523</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2827; 10252</t>
+          <t>2728; 10100</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13190; 25609</t>
+          <t>12905; 25581</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4383; 13721</t>
+          <t>3928; 12648</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2657</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>3716</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2727</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1420</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1214; 4171</t>
+          <t>0; 2744</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1398; 6027</t>
+          <t>1092; 5790</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>718; 5475</t>
+          <t>1270; 5939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3316</t>
+          <t>645; 4161</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1076; 5770</t>
+          <t>1396; 6506</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1245; 5858</t>
+          <t>684; 5354</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2012; 6259</t>
+          <t>1978; 6228</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3650; 10544</t>
+          <t>3738; 10849</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3253; 9595</t>
+          <t>3288; 9969</t>
         </is>
       </c>
     </row>
@@ -2511,27 +2511,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>10385</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25044</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16171</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>11156</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>27514</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>15016</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>10385</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>25044</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>16171</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6651; 17293</t>
+          <t>6182; 16118</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20800; 36540</t>
+          <t>17991; 33839</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9935; 21708</t>
+          <t>10391; 24300</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6124; 16677</t>
+          <t>6417; 16856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17902; 33282</t>
+          <t>20414; 36306</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10631; 23642</t>
+          <t>9486; 21906</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14609; 29907</t>
+          <t>15204; 29725</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>42257; 63283</t>
+          <t>42840; 64607</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23892; 41408</t>
+          <t>23635; 41133</t>
         </is>
       </c>
     </row>
